--- a/data/trans_dic/P56$amigo-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P56$amigo-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,42</t>
+          <t>0,0; 73,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,94</t>
+          <t>0,0; 27,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,65</t>
+          <t>0,0; 19,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,92</t>
+          <t>0,0; 26,16</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,72</t>
+          <t>0,0; 68,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,58</t>
+          <t>0,0; 42,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,52</t>
+          <t>0,0; 20,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 9,98</t>
+          <t>1,31; 11,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,76</t>
+          <t>0,0; 27,7</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,49</t>
+          <t>0,0; 16,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 13,9</t>
+          <t>2,22; 14,13</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,71</t>
+          <t>0,0; 36,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 11,12</t>
+          <t>1,19; 12,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,94</t>
+          <t>0,0; 36,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,74</t>
+          <t>0,77; 8,34</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,18</t>
+          <t>0,0; 27,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,01</t>
+          <t>0,0; 41,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,59</t>
+          <t>0,0; 18,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,28</t>
+          <t>0,0; 42,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,22</t>
+          <t>0,0; 14,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,08</t>
+          <t>0,0; 10,9</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,67</t>
+          <t>0,0; 26,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,25</t>
+          <t>0,0; 55,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,79</t>
+          <t>0,0; 11,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,44</t>
+          <t>0,0; 52,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,25</t>
+          <t>0,0; 10,87</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,62</t>
+          <t>0,0; 10,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 3,97</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,92</t>
+          <t>0,0; 16,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,55; 20,18</t>
+          <t>5,51; 20,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,69</t>
+          <t>0,0; 9,84</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0; 3,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,44; 17,07</t>
+          <t>4,31; 15,94</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,4</t>
+          <t>0,0; 31,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,92</t>
+          <t>0,0; 17,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,23</t>
+          <t>0,0; 5,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,54</t>
+          <t>0,0; 14,26</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,56</t>
+          <t>0,0; 12,97</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,14</t>
+          <t>0,0; 4,55</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,09; 16,78</t>
+          <t>2,1; 15,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,45; 8,24</t>
+          <t>1,61; 8,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,53</t>
+          <t>0,0; 7,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,93</t>
+          <t>1,01; 5,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,57</t>
+          <t>0,57; 4,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,0</t>
+          <t>2,31; 5,83</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,36; 7,32</t>
+          <t>1,39; 8,16</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,21</t>
+          <t>0,73; 4,22</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,84</t>
+          <t>0,4; 3,79</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,65</t>
+          <t>2,69; 5,81</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda sus amistades cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1276</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1639</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1441</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3441</t>
+          <t>0; 3684</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1366</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4871</t>
+          <t>0; 5938</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2176</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 973</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1564</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 6974</t>
+          <t>0; 5458</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 1927</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3834</t>
+          <t>0; 3467</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4040</t>
+          <t>0; 4741</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2194</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1449</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4463</t>
+          <t>0; 5127</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1854</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6465</t>
+          <t>0; 7621</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2404</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>546; 4182</t>
+          <t>549; 4655</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5130</t>
+          <t>0; 5980</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 6559</t>
+          <t>0; 7843</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2212</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1195; 7521</t>
+          <t>1204; 7645</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1303</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1923</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1397</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1092</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4498</t>
+          <t>0; 4487</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1923</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2236</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>390; 3728</t>
+          <t>398; 4237</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5306</t>
+          <t>0; 5525</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 2012</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 1986</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>402; 4010</t>
+          <t>398; 4323</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1146</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1802</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1570</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2614</t>
+          <t>0; 2584</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>0; 4438</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
           <t>0; 4543</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0; 1940</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0; 4384</t>
-        </is>
-      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 756</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4458</t>
+          <t>0; 5692</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 1979</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 5317</t>
+          <t>0; 4995</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 3217</t>
+          <t>0; 3167</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1309</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1772</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 616</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1926</t>
+          <t>0; 1951</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 1854</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1870</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6935</t>
+          <t>0; 6732</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 1955</t>
+          <t>0; 1899</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 1783</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 1934</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 6901</t>
+          <t>0; 6805</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2950</t>
+          <t>0; 2619</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1336</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1819</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1458</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 1589</t>
+          <t>0; 1794</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1976</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1917</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2329</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 669</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 1920</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 1960</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 2025</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 1735</t>
+          <t>0; 1915</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1370</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2098</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1894</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 1383</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 1433</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 5639</t>
+          <t>0; 5768</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2214</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2328; 8461</t>
+          <t>2308; 8434</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 1561</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 4941</t>
+          <t>0; 5015</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 2147</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2410; 9277</t>
+          <t>2340; 8659</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 6224</t>
+          <t>0; 6121</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2066</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 1706</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 1134</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 2112</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 5088</t>
+          <t>0; 5393</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 2273</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 3571</t>
+          <t>0; 3358</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 7147</t>
+          <t>0; 7009</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 4501</t>
+          <t>0; 5050</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 2168</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 3236</t>
+          <t>0; 3555</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1008; 8102</t>
+          <t>1013; 7266</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 2178</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0; 1748</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1478; 8413</t>
+          <t>1640; 8489</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0; 7043</t>
+          <t>0; 6632</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2156; 12176</t>
+          <t>2069; 12115</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>974; 9572</t>
+          <t>973; 8504</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5751; 15073</t>
+          <t>5800; 14629</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1926; 10378</t>
+          <t>1978; 11567</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2136; 11953</t>
+          <t>2062; 11962</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>996; 9353</t>
+          <t>978; 9233</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>8772; 19937</t>
+          <t>9491; 20514</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$amigo-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P56$amigo-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,24</t>
+          <t>0,0; 56,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,96</t>
+          <t>0,0; 25,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,29</t>
+          <t>0,0; 20,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,16</t>
+          <t>0,0; 25,82</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,91</t>
+          <t>0,0; 58,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,02</t>
+          <t>0,0; 47,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,65</t>
+          <t>0,0; 18,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,17 +892,17 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 11,11</t>
+          <t>1,28; 11,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,7</t>
+          <t>0,0; 23,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,13</t>
+          <t>0,0; 14,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 14,13</t>
+          <t>2,05; 13,37</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,62</t>
+          <t>0,0; 32,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 12,64</t>
+          <t>1,18; 12,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,38</t>
+          <t>0,0; 27,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 8,34</t>
+          <t>0,77; 8,26</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,85</t>
+          <t>0,0; 28,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,04</t>
+          <t>0,0; 51,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,23</t>
+          <t>0,0; 24,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,5</t>
+          <t>0,0; 34,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,3</t>
+          <t>0,0; 11,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,9</t>
+          <t>0,0; 10,32</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,0</t>
+          <t>0,0; 26,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1307,12 +1307,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,57</t>
+          <t>0,0; 53,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,45</t>
+          <t>0,0; 11,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1327,12 +1327,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,7</t>
+          <t>0,0; 52,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,87</t>
+          <t>0,0; 10,78</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,86</t>
+          <t>0,0; 12,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,97</t>
+          <t>0,0; 4,15</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,28</t>
+          <t>0,0; 18,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,51; 20,12</t>
+          <t>5,07; 18,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,84</t>
+          <t>0,0; 10,6</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,31; 15,94</t>
+          <t>3,92; 14,7</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,86</t>
+          <t>0,0; 32,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,94</t>
+          <t>0,0; 18,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1732,17 +1732,17 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,86</t>
+          <t>0,0; 5,98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,26</t>
+          <t>0,0; 12,76</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,97</t>
+          <t>0,0; 13,89</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,55</t>
+          <t>0,0; 4,18</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,1; 15,05</t>
+          <t>2,1; 15,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1852,47 +1852,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,61; 8,32</t>
+          <t>1,39; 8,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,09</t>
+          <t>0,0; 7,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,9</t>
+          <t>0,96; 5,8</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,95</t>
+          <t>0,56; 4,91</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,83</t>
+          <t>2,37; 6,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,16</t>
+          <t>1,37; 7,98</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,22</t>
+          <t>0,74; 4,18</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,79</t>
+          <t>0,4; 3,74</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,69; 5,81</t>
+          <t>2,45; 5,58</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>688</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>688</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3684</t>
+          <t>0; 2992</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5938</t>
+          <t>0; 5455</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5458</t>
+          <t>0; 5765</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3467</t>
+          <t>0; 3543</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3482</t>
+          <t>3630</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4741</t>
+          <t>0; 4028</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5127</t>
+          <t>0; 6183</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 7621</t>
+          <t>0; 6789</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2452,17 +2452,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>549; 4655</t>
+          <t>573; 4962</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5980</t>
+          <t>0; 5108</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 7843</t>
+          <t>0; 7183</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1204; 7645</t>
+          <t>1187; 7726</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1510</t>
         </is>
       </c>
     </row>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4487</t>
+          <t>0; 3994</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>398; 4237</t>
+          <t>397; 4223</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5525</t>
+          <t>0; 4203</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>398; 4323</t>
+          <t>397; 4249</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>616</t>
         </is>
       </c>
     </row>
@@ -2848,12 +2848,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2584</t>
+          <t>0; 2747</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4438</t>
+          <t>0; 5593</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4543</t>
+          <t>0; 6062</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5692</t>
+          <t>0; 4639</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2883,12 +2883,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 4995</t>
+          <t>0; 4159</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 3167</t>
+          <t>0; 3131</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>483</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>870</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1951</t>
+          <t>0; 2000</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6732</t>
+          <t>0; 6430</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 1899</t>
+          <t>0; 1908</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 6805</t>
+          <t>0; 6755</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2619</t>
+          <t>0; 2683</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>406</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>406</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 1794</t>
+          <t>0; 2030</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 1915</t>
+          <t>0; 2036</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>5355</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 5768</t>
+          <t>0; 6428</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2308; 8434</t>
+          <t>2617; 9695</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 5015</t>
+          <t>0; 5402</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2340; 8659</t>
+          <t>2609; 9785</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1209</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 6121</t>
+          <t>0; 6193</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 5393</t>
+          <t>0; 5428</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3700,17 +3700,17 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 3358</t>
+          <t>0; 3974</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 7009</t>
+          <t>0; 6270</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 5050</t>
+          <t>0; 5411</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 3555</t>
+          <t>0; 3769</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>14284</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1013; 7266</t>
+          <t>1012; 7720</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3888,47 +3888,47 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1640; 8489</t>
+          <t>1506; 8681</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0; 6632</t>
+          <t>0; 6763</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2069; 12115</t>
+          <t>1976; 11896</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>973; 8504</t>
+          <t>965; 8435</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5800; 14629</t>
+          <t>6525; 16865</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1978; 11567</t>
+          <t>1937; 11320</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2062; 11962</t>
+          <t>2090; 11859</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>978; 9233</t>
+          <t>977; 9130</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>9491; 20514</t>
+          <t>9414; 21425</t>
         </is>
       </c>
     </row>
